--- a/Result/profitability/8924.xlsx
+++ b/Result/profitability/8924.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.28</v>
       </c>
       <c r="M2" t="n">
-        <v>1.175</v>
+        <v>0.96</v>
       </c>
       <c r="N2" t="n">
-        <v>17.1775</v>
+        <v>16.08</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -693,7 +693,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>97.09999999999999</v>
@@ -780,10 +780,10 @@
         <v>0.62</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11625</v>
+        <v>0.87</v>
       </c>
       <c r="N3" t="n">
-        <v>17.7275</v>
+        <v>16.56625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>97.2</v>
@@ -899,10 +899,10 @@
         <v>0.77</v>
       </c>
       <c r="M4" t="n">
-        <v>1.045</v>
+        <v>0.88125</v>
       </c>
       <c r="N4" t="n">
-        <v>18.10125</v>
+        <v>16.6325</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>97.3</v>
@@ -1018,10 +1018,10 @@
         <v>2.03</v>
       </c>
       <c r="M5" t="n">
-        <v>1.21375</v>
+        <v>0.9312499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>18.75125</v>
+        <v>17.44375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01375</v>
+        <v>0.7224999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>17.74375</v>
+        <v>16.04875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>98.09999999999999</v>
@@ -1264,13 +1264,13 @@
         <v>0.54</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8687499999999999</v>
+        <v>0.5862499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>17.795</v>
+        <v>16</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,13 +1282,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>0.39</v>
       </c>
       <c r="M8" t="n">
-        <v>0.71375</v>
+        <v>0.62875</v>
       </c>
       <c r="N8" t="n">
-        <v>17.705</v>
+        <v>16.9775</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -1772,7 +1772,7 @@
         <v>0.43</v>
       </c>
       <c r="M11" t="n">
-        <v>0.67375</v>
+        <v>0.6737500000000001</v>
       </c>
       <c r="N11" t="n">
         <v>16.55875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8924</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D75" t="n">
+        <v>948</v>
+      </c>
+      <c r="E75" t="n">
+        <v>57</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-39</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-3.92%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-35</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-53</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.9362500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.9325</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-13.6</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.82</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.5060869565217392</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.386503067484663</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-10.46</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.6480793060718711</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
